--- a/ExcelBasics/Student.xlsx
+++ b/ExcelBasics/Student.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TYCS\DS\ExcelBasics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBE3AD4F-8528-446B-96C1-A852DAA76905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D472E36B-C566-48D0-BB93-F53939ACDF88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="4" activeTab="5" xr2:uid="{657B381F-FBFC-4ACC-A378-763791E0E993}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="5" xr2:uid="{657B381F-FBFC-4ACC-A378-763791E0E993}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId7"/>
+    <pivotCache cacheId="0" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -164,7 +164,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="175" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -297,7 +297,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment shrinkToFit="1"/>
@@ -308,22 +308,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -338,14 +336,14 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1582,7 +1580,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{31C88F63-9F43-4A86-8AAE-CF4BFB3CFB71}" name="PivotTable1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{31C88F63-9F43-4A86-8AAE-CF4BFB3CFB71}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="E7:G14" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField dataField="1" showAll="0"/>
@@ -2331,7 +2329,7 @@
       <c r="C1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="7"/>
+      <c r="D1" s="6"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
@@ -2398,7 +2396,7 @@
       <c r="C7" s="2">
         <v>75</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
@@ -2409,79 +2407,79 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8">
         <v>3</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8">
         <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9">
         <v>5</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G9">
         <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10">
         <v>1</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G10">
         <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11">
         <v>6</v>
       </c>
-      <c r="G11" s="4">
+      <c r="G11">
         <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12">
         <v>4</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G12">
         <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13">
         <v>2</v>
       </c>
-      <c r="G13" s="4">
+      <c r="G13">
         <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14">
         <v>21</v>
       </c>
-      <c r="G14" s="4">
+      <c r="G14">
         <v>525</v>
       </c>
     </row>
@@ -2512,7 +2510,7 @@
       <c r="E1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2625,128 +2623,127 @@
   <sheetData>
     <row r="1" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
     </row>
     <row r="3" spans="2:6" ht="15.6" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="17" t="s">
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F3" s="15" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="4" spans="2:6" ht="21.6" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="19" t="s">
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="E4" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="17" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
     </row>
     <row r="6" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="13"/>
-      <c r="C6" s="13" t="s">
+      <c r="B6" s="11"/>
+      <c r="C6" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6">
         <v>70</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="16">
         <v>80</v>
       </c>
-      <c r="F6" s="18">
+      <c r="F6" s="16">
         <v>95</v>
       </c>
     </row>
     <row r="7" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="13"/>
-      <c r="C7" s="13" t="s">
+      <c r="B7" s="11"/>
+      <c r="C7" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7">
         <v>20</v>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="16">
         <v>25</v>
       </c>
-      <c r="F7" s="18">
+      <c r="F7" s="16">
         <v>30</v>
       </c>
     </row>
     <row r="8" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="13"/>
-      <c r="C8" s="13" t="s">
+      <c r="B8" s="11"/>
+      <c r="C8" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8">
         <v>10</v>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="16">
         <v>20</v>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="16">
         <v>25</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="14"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
     </row>
     <row r="10" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="13"/>
-      <c r="C10" s="13" t="s">
+      <c r="B10" s="11"/>
+      <c r="C10" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10">
         <v>100</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10">
         <v>125</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10">
         <v>150</v>
       </c>
     </row>
     <row r="11" spans="2:6" ht="15" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="15"/>
-      <c r="C11" s="15" t="s">
+      <c r="B11" s="13"/>
+      <c r="C11" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="7">
         <v>33.3333333333333</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="7">
         <v>41.6666666666667</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11" s="7">
         <v>50</v>
       </c>
     </row>
@@ -2787,9 +2784,9 @@
         <v>6</v>
       </c>
       <c r="C1" s="2"/>
-      <c r="D1" s="20">
+      <c r="D1" s="18">
         <f>per</f>
-        <v>53.333333333333336</v>
+        <v>60</v>
       </c>
       <c r="E1">
         <v>15</v>
@@ -2806,21 +2803,21 @@
         <v>16</v>
       </c>
       <c r="B2" s="3">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2">
         <v>60</v>
       </c>
-      <c r="E2" s="21">
-        <f t="dataTable" ref="E2:G6" dt2D="1" dtr="1" r1="B3" r2="B2"/>
-        <v>31.666666666666664</v>
-      </c>
-      <c r="F2" s="21">
-        <v>33.333333333333329</v>
-      </c>
-      <c r="G2" s="21">
-        <v>35</v>
+      <c r="E2" s="19">
+        <f t="dataTable" ref="E2:G6" dt2D="1" dtr="1" r1="B4" r2="B3"/>
+        <v>71.666666666666671</v>
+      </c>
+      <c r="F2" s="19">
+        <v>73.333333333333329</v>
+      </c>
+      <c r="G2" s="19">
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -2834,14 +2831,14 @@
       <c r="D3">
         <v>70</v>
       </c>
-      <c r="E3" s="21">
-        <v>35</v>
-      </c>
-      <c r="F3" s="21">
-        <v>36.666666666666664</v>
-      </c>
-      <c r="G3" s="21">
-        <v>38.333333333333336</v>
+      <c r="E3" s="19">
+        <v>75</v>
+      </c>
+      <c r="F3" s="19">
+        <v>76.666666666666671</v>
+      </c>
+      <c r="G3" s="19">
+        <v>78.333333333333329</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -2855,14 +2852,14 @@
       <c r="D4">
         <v>80</v>
       </c>
-      <c r="E4" s="21">
-        <v>38.333333333333336</v>
-      </c>
-      <c r="F4" s="21">
-        <v>40</v>
-      </c>
-      <c r="G4" s="21">
-        <v>41.666666666666671</v>
+      <c r="E4" s="19">
+        <v>78.333333333333329</v>
+      </c>
+      <c r="F4" s="19">
+        <v>80</v>
+      </c>
+      <c r="G4" s="19">
+        <v>81.666666666666671</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -2871,20 +2868,20 @@
       </c>
       <c r="B5" s="3">
         <f>SUM(B2:B4)</f>
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5">
         <v>90</v>
       </c>
-      <c r="E5" s="21">
-        <v>41.666666666666671</v>
-      </c>
-      <c r="F5" s="21">
-        <v>43.333333333333336</v>
-      </c>
-      <c r="G5" s="21">
-        <v>45</v>
+      <c r="E5" s="19">
+        <v>81.666666666666671</v>
+      </c>
+      <c r="F5" s="19">
+        <v>83.333333333333343</v>
+      </c>
+      <c r="G5" s="19">
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -2893,20 +2890,20 @@
       </c>
       <c r="B6" s="3">
         <f>B5/300*100</f>
-        <v>53.333333333333336</v>
+        <v>60</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6">
         <v>100</v>
       </c>
-      <c r="E6" s="21">
-        <v>45</v>
-      </c>
-      <c r="F6" s="21">
-        <v>46.666666666666664</v>
-      </c>
-      <c r="G6" s="21">
-        <v>48.333333333333336</v>
+      <c r="E6" s="19">
+        <v>85</v>
+      </c>
+      <c r="F6" s="19">
+        <v>86.666666666666671</v>
+      </c>
+      <c r="G6" s="19">
+        <v>88.333333333333329</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -2915,8 +2912,8 @@
       <c r="C7" s="2"/>
     </row>
   </sheetData>
-  <scenarios current="1" show="1" sqref="B5:B6">
-    <scenario name="Avg performance" locked="1" count="3" user="user" comment="Created by user on 04-09-2026">
+  <scenarios current="0" show="1" sqref="B5:B6">
+    <scenario name="Avg performance" locked="1" count="3" user="user" comment="Created by user on 04-09-2026_x000a_Modified by user on 07-09-2026">
       <inputCells r="B2" val="80"/>
       <inputCells r="B3" val="25"/>
       <inputCells r="B4" val="20"/>
